--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEW_JERSEY_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEW_JERSEY_2017.xlsx
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C203">
@@ -8005,7 +8005,7 @@
         <v>14</v>
       </c>
       <c r="D425">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="426">
@@ -9715,7 +9715,7 @@
         <v>14</v>
       </c>
       <c r="D520">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="521">
@@ -11688,14 +11688,14 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C630">
         <v>14</v>
       </c>
       <c r="D630">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="631">
@@ -12271,7 +12271,7 @@
         <v>14</v>
       </c>
       <c r="D662">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="663">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C689">
@@ -14935,7 +14935,7 @@
         <v>14</v>
       </c>
       <c r="D810">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="811">
@@ -15511,7 +15511,7 @@
         <v>14</v>
       </c>
       <c r="D842">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="843">
@@ -16861,7 +16861,7 @@
         <v>14</v>
       </c>
       <c r="D917">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="918">
@@ -18661,7 +18661,7 @@
         <v>14</v>
       </c>
       <c r="D1017">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="1018">
@@ -18679,7 +18679,7 @@
         <v>14</v>
       </c>
       <c r="D1018">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="1019">
@@ -20191,7 +20191,7 @@
         <v>14</v>
       </c>
       <c r="D1102">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="1103">
@@ -22333,7 +22333,7 @@
         <v>14</v>
       </c>
       <c r="D1221">
-        <v>0.0009348290598290599</v>
+        <v>0.00093482905982906</v>
       </c>
     </row>
     <row r="1222">
